--- a/lab-01-bright-leaf/topology-documentation.xlsx
+++ b/lab-01-bright-leaf/topology-documentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SICKBOY\Documents\networking-with-chuck\Labs\lab-01-bright-leaf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37320697-1084-4F95-9F04-6F2594717E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D822B46F-1C64-43D4-A967-A6E43111C478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{23643CF5-7BF7-4D3D-9BDF-050AC057401B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="113">
   <si>
     <t>Device Name</t>
   </si>
@@ -168,9 +168,6 @@
     <t>Allocated hosts</t>
   </si>
   <si>
-    <t>VLAN 50</t>
-  </si>
-  <si>
     <t>SVI</t>
   </si>
   <si>
@@ -189,9 +186,6 @@
     <t>00:D0:BA:71:77:02</t>
   </si>
   <si>
-    <t>vlan50</t>
-  </si>
-  <si>
     <t>00:30:F2:56:82:4B</t>
   </si>
   <si>
@@ -367,6 +361,9 @@
   </si>
   <si>
     <t>216.0.5.49 /30</t>
+  </si>
+  <si>
+    <t>vlan30</t>
   </si>
 </sst>
 </file>
@@ -455,11 +452,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -469,12 +468,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -789,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0704781D-1F84-4D21-9814-7A7941AAC2EC}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
@@ -852,7 +845,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -867,12 +860,12 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -892,7 +885,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
@@ -904,7 +897,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -919,12 +912,11 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -944,7 +936,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
@@ -956,7 +948,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -971,12 +963,11 @@
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>112</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1060,8 +1051,8 @@
       <c r="J15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>98</v>
+      <c r="K15" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -1096,7 +1087,7 @@
         <v>42</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -1131,7 +1122,7 @@
         <v>43</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -1166,34 +1157,34 @@
         <v>44</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="C19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1207,10 +1198,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1223,263 +1214,259 @@
       <c r="K21" s="3"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
+      <c r="A24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="10"/>
+        <v>89</v>
+      </c>
+      <c r="C40" s="4"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="11"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
+      <c r="A42" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="1"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D43" s="1"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>111</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>95</v>
+        <v>109</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
-      <c r="B45" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>96</v>
+      <c r="B45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
-      <c r="B46" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>97</v>
+      <c r="B46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
-      <c r="B47" s="12" t="s">
-        <v>76</v>
+      <c r="B47" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="7"/>
-      <c r="B51" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
